--- a/HIBERNATE_MAPPING.xlsx
+++ b/HIBERNATE_MAPPING.xlsx
@@ -4,19 +4,20 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="o2m Delete Entity" sheetId="1" r:id="rId1"/>
     <sheet name="m2m" sheetId="3" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="85">
   <si>
     <t>impl1</t>
   </si>
@@ -317,6 +318,42 @@
   </si>
   <si>
     <t>Student API</t>
+  </si>
+  <si>
+    <t>Isolation Level</t>
+  </si>
+  <si>
+    <t>Dirty Read</t>
+  </si>
+  <si>
+    <t>Non-Repeatable Read</t>
+  </si>
+  <si>
+    <t>Phantom Read</t>
+  </si>
+  <si>
+    <t>READ_UNCOMMITTED</t>
+  </si>
+  <si>
+    <t>READ_COMMITTED</t>
+  </si>
+  <si>
+    <t>REPEATABLE_READ</t>
+  </si>
+  <si>
+    <t>SERIALIZABLE</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no </t>
+  </si>
+  <si>
+    <t>DEFAULT</t>
   </si>
 </sst>
 </file>
@@ -429,7 +466,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="52">
+  <borders count="53">
     <border>
       <left/>
       <right/>
@@ -1106,11 +1143,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1421,6 +1467,66 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1429,8 +1535,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <colors>
     <mruColors>
+      <color rgb="FF006600"/>
       <color rgb="FF0000FF"/>
-      <color rgb="FF006600"/>
     </mruColors>
   </colors>
   <extLst>
@@ -2423,4 +2529,102 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:E7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="128"/>
+    <col min="2" max="2" width="21" style="128" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" style="128" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" style="128" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" style="128" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="128"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="133" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="131" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2" s="131" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" s="132" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="134" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="129"/>
+      <c r="D3" s="129"/>
+      <c r="E3" s="130"/>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B4" s="135" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" s="143" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" s="144" t="s">
+        <v>81</v>
+      </c>
+      <c r="E4" s="145" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="136" t="s">
+        <v>78</v>
+      </c>
+      <c r="C5" s="139" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" s="146" t="s">
+        <v>81</v>
+      </c>
+      <c r="E5" s="147" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6" s="136" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="139" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" s="138" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" s="147" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="137" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" s="140" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7" s="141" t="s">
+        <v>82</v>
+      </c>
+      <c r="E7" s="142" t="s">
+        <v>82</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/HIBERNATE_MAPPING.xlsx
+++ b/HIBERNATE_MAPPING.xlsx
@@ -1476,9 +1476,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1525,6 +1522,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2546,21 +2546,21 @@
   <sheetData>
     <row r="1" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="133" t="s">
+      <c r="B2" s="132" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="131" t="s">
+      <c r="C2" s="147" t="s">
         <v>74</v>
       </c>
-      <c r="D2" s="131" t="s">
+      <c r="D2" s="147" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="132" t="s">
+      <c r="E2" s="131" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="3" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="134" t="s">
+      <c r="B3" s="133" t="s">
         <v>84</v>
       </c>
       <c r="C3" s="129"/>
@@ -2568,58 +2568,58 @@
       <c r="E3" s="130"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="135" t="s">
+      <c r="B4" s="134" t="s">
         <v>77</v>
       </c>
-      <c r="C4" s="143" t="s">
+      <c r="C4" s="142" t="s">
         <v>81</v>
       </c>
-      <c r="D4" s="144" t="s">
+      <c r="D4" s="143" t="s">
         <v>81</v>
       </c>
-      <c r="E4" s="145" t="s">
+      <c r="E4" s="144" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="136" t="s">
+      <c r="B5" s="135" t="s">
         <v>78</v>
       </c>
-      <c r="C5" s="139" t="s">
+      <c r="C5" s="138" t="s">
         <v>82</v>
       </c>
-      <c r="D5" s="146" t="s">
+      <c r="D5" s="145" t="s">
         <v>81</v>
       </c>
-      <c r="E5" s="147" t="s">
+      <c r="E5" s="146" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" s="136" t="s">
+      <c r="B6" s="135" t="s">
         <v>79</v>
       </c>
-      <c r="C6" s="139" t="s">
+      <c r="C6" s="138" t="s">
         <v>82</v>
       </c>
-      <c r="D6" s="138" t="s">
+      <c r="D6" s="137" t="s">
         <v>83</v>
       </c>
-      <c r="E6" s="147" t="s">
+      <c r="E6" s="146" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="7" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="137" t="s">
+      <c r="B7" s="136" t="s">
         <v>80</v>
       </c>
-      <c r="C7" s="140" t="s">
+      <c r="C7" s="139" t="s">
         <v>82</v>
       </c>
-      <c r="D7" s="141" t="s">
+      <c r="D7" s="140" t="s">
         <v>82</v>
       </c>
-      <c r="E7" s="142" t="s">
+      <c r="E7" s="141" t="s">
         <v>82</v>
       </c>
     </row>
